--- a/FPSDemo/MiniTemplate/Datas/#enemy_spawn_pool.xlsx
+++ b/FPSDemo/MiniTemplate/Datas/#enemy_spawn_pool.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="enemy_spawn_pool" sheetId="1" r:id="R8b066b40f5184e03"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="enemy_spawn_pool" sheetId="1" r:id="R27e692c0dee24c39"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -646,7 +646,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="K5" s="2" t="n">
-        <x:v>100</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="L5" s="2" t="n">
         <x:v>100</x:v>
@@ -658,25 +658,25 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="O5" s="2" t="n">
-        <x:v>0.04</x:v>
+        <x:v>0.06</x:v>
       </x:c>
       <x:c r="P5" s="2" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="Q5" s="2" t="n">
-        <x:v>1.15</x:v>
+        <x:v>1.18</x:v>
       </x:c>
       <x:c r="R5" s="2" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="S5" s="2" t="n">
-        <x:v>0.02</x:v>
+        <x:v>0.035</x:v>
       </x:c>
       <x:c r="T5" s="2" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="U5" s="2" t="n">
-        <x:v>1.08</x:v>
+        <x:v>1.1</x:v>
       </x:c>
       <x:c r="V5" s="2" t="n">
         <x:v>1</x:v>
@@ -694,13 +694,13 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="AA5" s="2" t="n">
-        <x:v>0.03</x:v>
+        <x:v>0.04</x:v>
       </x:c>
       <x:c r="AB5" s="2" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="AC5" s="2" t="n">
-        <x:v>1.1</x:v>
+        <x:v>1.12</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -724,40 +724,40 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="H6" s="2" t="n">
-        <x:v>100</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="I6" s="2" t="n">
-        <x:v>0</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="J6" s="2" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="K6" s="2" t="n">
-        <x:v>100</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="L6" s="2" t="n">
-        <x:v>100</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="M6" s="2" t="n">
-        <x:v>4</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="N6" s="2" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="O6" s="2" t="n">
-        <x:v>0.04</x:v>
+        <x:v>0.05</x:v>
       </x:c>
       <x:c r="P6" s="2" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="Q6" s="2" t="n">
-        <x:v>1.12</x:v>
+        <x:v>1.15</x:v>
       </x:c>
       <x:c r="R6" s="2" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="S6" s="2" t="n">
-        <x:v>0.02</x:v>
+        <x:v>0.03</x:v>
       </x:c>
       <x:c r="T6" s="2" t="n">
         <x:v>0</x:v>
@@ -769,25 +769,25 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="W6" s="2" t="n">
-        <x:v>0.01</x:v>
+        <x:v>0.005</x:v>
       </x:c>
       <x:c r="X6" s="2" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="Y6" s="2" t="n">
-        <x:v>1.04</x:v>
+        <x:v>1.02</x:v>
       </x:c>
       <x:c r="Z6" s="2" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="AA6" s="2" t="n">
-        <x:v>0.03</x:v>
+        <x:v>0.04</x:v>
       </x:c>
       <x:c r="AB6" s="2" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="AC6" s="2" t="n">
-        <x:v>1.1</x:v>
+        <x:v>1.12</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -811,22 +811,22 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="H7" s="2" t="n">
-        <x:v>100</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="I7" s="2" t="n">
-        <x:v>0</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="J7" s="2" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="K7" s="2" t="n">
-        <x:v>100</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="L7" s="2" t="n">
-        <x:v>100</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="M7" s="2" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="N7" s="2" t="n">
         <x:v>1</x:v>
@@ -838,19 +838,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="Q7" s="2" t="n">
-        <x:v>1.12</x:v>
+        <x:v>1.1</x:v>
       </x:c>
       <x:c r="R7" s="2" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="S7" s="2" t="n">
-        <x:v>0.02</x:v>
+        <x:v>0.025</x:v>
       </x:c>
       <x:c r="T7" s="2" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="U7" s="2" t="n">
-        <x:v>1.08</x:v>
+        <x:v>1.07</x:v>
       </x:c>
       <x:c r="V7" s="2" t="n">
         <x:v>1</x:v>
@@ -868,13 +868,13 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="AA7" s="2" t="n">
-        <x:v>0.03</x:v>
+        <x:v>0.05</x:v>
       </x:c>
       <x:c r="AB7" s="2" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="AC7" s="2" t="n">
-        <x:v>1.1</x:v>
+        <x:v>1.15</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -898,70 +898,70 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="H8" s="2" t="n">
-        <x:v>70</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="I8" s="2" t="n">
-        <x:v>-2</x:v>
+        <x:v>-3</x:v>
       </x:c>
       <x:c r="J8" s="2" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="K8" s="2" t="n">
-        <x:v>70</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="L8" s="2" t="n">
-        <x:v>70</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="M8" s="2" t="n">
-        <x:v>12</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="N8" s="2" t="n">
-        <x:v>1.1</x:v>
+        <x:v>1.05</x:v>
       </x:c>
       <x:c r="O8" s="2" t="n">
-        <x:v>0.05</x:v>
+        <x:v>0.07</x:v>
       </x:c>
       <x:c r="P8" s="2" t="n">
-        <x:v>0</x:v>
+        <x:v>0.1</x:v>
       </x:c>
       <x:c r="Q8" s="2" t="n">
-        <x:v>1.35</x:v>
+        <x:v>1.65</x:v>
       </x:c>
       <x:c r="R8" s="2" t="n">
         <x:v>1.05</x:v>
       </x:c>
       <x:c r="S8" s="2" t="n">
-        <x:v>0.03</x:v>
+        <x:v>0.05</x:v>
       </x:c>
       <x:c r="T8" s="2" t="n">
-        <x:v>0</x:v>
+        <x:v>0.06</x:v>
       </x:c>
       <x:c r="U8" s="2" t="n">
-        <x:v>1.2</x:v>
+        <x:v>1.5</x:v>
       </x:c>
       <x:c r="V8" s="2" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="W8" s="2" t="n">
-        <x:v>0.01</x:v>
+        <x:v>0.012</x:v>
       </x:c>
       <x:c r="X8" s="2" t="n">
-        <x:v>0</x:v>
+        <x:v>0.02</x:v>
       </x:c>
       <x:c r="Y8" s="2" t="n">
-        <x:v>1.05</x:v>
+        <x:v>1.16</x:v>
       </x:c>
       <x:c r="Z8" s="2" t="n">
         <x:v>1.1</x:v>
       </x:c>
       <x:c r="AA8" s="2" t="n">
-        <x:v>0.05</x:v>
+        <x:v>0.06</x:v>
       </x:c>
       <x:c r="AB8" s="2" t="n">
-        <x:v>0</x:v>
+        <x:v>0.06</x:v>
       </x:c>
       <x:c r="AC8" s="2" t="n">
-        <x:v>1.3</x:v>
+        <x:v>1.55</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -985,46 +985,46 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="H9" s="2" t="n">
-        <x:v>45</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="I9" s="2" t="n">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="J9" s="2" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="K9" s="2" t="n">
-        <x:v>55</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="L9" s="2" t="n">
-        <x:v>45</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="M9" s="2" t="n">
-        <x:v>6</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="N9" s="2" t="n">
-        <x:v>1</x:v>
+        <x:v>1.1</x:v>
       </x:c>
       <x:c r="O9" s="2" t="n">
+        <x:v>0.07</x:v>
+      </x:c>
+      <x:c r="P9" s="2" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="Q9" s="2" t="n">
+        <x:v>1.65</x:v>
+      </x:c>
+      <x:c r="R9" s="2" t="n">
+        <x:v>1.1</x:v>
+      </x:c>
+      <x:c r="S9" s="2" t="n">
         <x:v>0.05</x:v>
       </x:c>
-      <x:c r="P9" s="2" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="Q9" s="2" t="n">
-        <x:v>1.35</x:v>
-      </x:c>
-      <x:c r="R9" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="S9" s="2" t="n">
-        <x:v>0.03</x:v>
-      </x:c>
       <x:c r="T9" s="2" t="n">
-        <x:v>0</x:v>
+        <x:v>0.06</x:v>
       </x:c>
       <x:c r="U9" s="2" t="n">
-        <x:v>1.18</x:v>
+        <x:v>1.5</x:v>
       </x:c>
       <x:c r="V9" s="2" t="n">
         <x:v>1</x:v>
@@ -1033,22 +1033,22 @@
         <x:v>0.01</x:v>
       </x:c>
       <x:c r="X9" s="2" t="n">
-        <x:v>0</x:v>
+        <x:v>0.02</x:v>
       </x:c>
       <x:c r="Y9" s="2" t="n">
-        <x:v>1.05</x:v>
+        <x:v>1.18</x:v>
       </x:c>
       <x:c r="Z9" s="2" t="n">
-        <x:v>1</x:v>
+        <x:v>1.1</x:v>
       </x:c>
       <x:c r="AA9" s="2" t="n">
-        <x:v>0.04</x:v>
+        <x:v>0.06</x:v>
       </x:c>
       <x:c r="AB9" s="2" t="n">
-        <x:v>0</x:v>
+        <x:v>0.06</x:v>
       </x:c>
       <x:c r="AC9" s="2" t="n">
-        <x:v>1.2</x:v>
+        <x:v>1.5</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -1072,7 +1072,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="H10" s="2" t="n">
-        <x:v>24</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="I10" s="2" t="n">
         <x:v>2</x:v>
@@ -1081,61 +1081,61 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="K10" s="2" t="n">
-        <x:v>34</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="L10" s="2" t="n">
-        <x:v>24</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="M10" s="2" t="n">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="N10" s="2" t="n">
-        <x:v>1</x:v>
+        <x:v>1.15</x:v>
       </x:c>
       <x:c r="O10" s="2" t="n">
-        <x:v>0.05</x:v>
+        <x:v>0.06</x:v>
       </x:c>
       <x:c r="P10" s="2" t="n">
-        <x:v>0</x:v>
+        <x:v>0.12</x:v>
       </x:c>
       <x:c r="Q10" s="2" t="n">
-        <x:v>1.35</x:v>
+        <x:v>1.8</x:v>
       </x:c>
       <x:c r="R10" s="2" t="n">
-        <x:v>1</x:v>
+        <x:v>1.15</x:v>
       </x:c>
       <x:c r="S10" s="2" t="n">
-        <x:v>0.03</x:v>
+        <x:v>0.045</x:v>
       </x:c>
       <x:c r="T10" s="2" t="n">
-        <x:v>0</x:v>
+        <x:v>0.08</x:v>
       </x:c>
       <x:c r="U10" s="2" t="n">
-        <x:v>1.18</x:v>
+        <x:v>1.65</x:v>
       </x:c>
       <x:c r="V10" s="2" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="W10" s="2" t="n">
-        <x:v>0</x:v>
+        <x:v>0.005</x:v>
       </x:c>
       <x:c r="X10" s="2" t="n">
-        <x:v>0</x:v>
+        <x:v>0.015</x:v>
       </x:c>
       <x:c r="Y10" s="2" t="n">
-        <x:v>1</x:v>
+        <x:v>1.08</x:v>
       </x:c>
       <x:c r="Z10" s="2" t="n">
-        <x:v>1</x:v>
+        <x:v>1.15</x:v>
       </x:c>
       <x:c r="AA10" s="2" t="n">
-        <x:v>0.04</x:v>
+        <x:v>0.07</x:v>
       </x:c>
       <x:c r="AB10" s="2" t="n">
-        <x:v>0</x:v>
+        <x:v>0.08</x:v>
       </x:c>
       <x:c r="AC10" s="2" t="n">
-        <x:v>1.25</x:v>
+        <x:v>1.7</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -1159,70 +1159,70 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="H11" s="2" t="n">
-        <x:v>50</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="I11" s="2" t="n">
         <x:v>-2</x:v>
       </x:c>
       <x:c r="J11" s="2" t="n">
-        <x:v>0</x:v>
+        <x:v>-3</x:v>
       </x:c>
       <x:c r="K11" s="2" t="n">
-        <x:v>50</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="L11" s="2" t="n">
-        <x:v>50</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="M11" s="2" t="n">
-        <x:v>16</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="N11" s="2" t="n">
-        <x:v>1.3</x:v>
+        <x:v>1.2</x:v>
       </x:c>
       <x:c r="O11" s="2" t="n">
-        <x:v>0.06</x:v>
+        <x:v>0.09</x:v>
       </x:c>
       <x:c r="P11" s="2" t="n">
-        <x:v>0.08</x:v>
+        <x:v>0.15</x:v>
       </x:c>
       <x:c r="Q11" s="2" t="n">
-        <x:v>1.8</x:v>
+        <x:v>2.6</x:v>
       </x:c>
       <x:c r="R11" s="2" t="n">
         <x:v>1.15</x:v>
       </x:c>
       <x:c r="S11" s="2" t="n">
-        <x:v>0.035</x:v>
+        <x:v>0.06</x:v>
       </x:c>
       <x:c r="T11" s="2" t="n">
-        <x:v>0.04</x:v>
+        <x:v>0.08</x:v>
       </x:c>
       <x:c r="U11" s="2" t="n">
-        <x:v>1.5</x:v>
+        <x:v>2.1</x:v>
       </x:c>
       <x:c r="V11" s="2" t="n">
-        <x:v>1.05</x:v>
+        <x:v>1.04</x:v>
       </x:c>
       <x:c r="W11" s="2" t="n">
-        <x:v>0.01</x:v>
+        <x:v>0.015</x:v>
       </x:c>
       <x:c r="X11" s="2" t="n">
-        <x:v>0</x:v>
+        <x:v>0.02</x:v>
       </x:c>
       <x:c r="Y11" s="2" t="n">
-        <x:v>1.15</x:v>
+        <x:v>1.22</x:v>
       </x:c>
       <x:c r="Z11" s="2" t="n">
         <x:v>1.25</x:v>
       </x:c>
       <x:c r="AA11" s="2" t="n">
-        <x:v>0.05</x:v>
+        <x:v>0.07</x:v>
       </x:c>
       <x:c r="AB11" s="2" t="n">
-        <x:v>0.05</x:v>
+        <x:v>0.08</x:v>
       </x:c>
       <x:c r="AC11" s="2" t="n">
-        <x:v>1.8</x:v>
+        <x:v>2.2</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
@@ -1246,70 +1246,70 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="H12" s="2" t="n">
-        <x:v>48</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="I12" s="2" t="n">
-        <x:v>1</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="J12" s="2" t="n">
-        <x:v>0</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="K12" s="2" t="n">
-        <x:v>58</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="L12" s="2" t="n">
-        <x:v>48</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="M12" s="2" t="n">
-        <x:v>9</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="N12" s="2" t="n">
         <x:v>1.25</x:v>
       </x:c>
       <x:c r="O12" s="2" t="n">
+        <x:v>0.09</x:v>
+      </x:c>
+      <x:c r="P12" s="2" t="n">
+        <x:v>0.15</x:v>
+      </x:c>
+      <x:c r="Q12" s="2" t="n">
+        <x:v>2.5</x:v>
+      </x:c>
+      <x:c r="R12" s="2" t="n">
+        <x:v>1.2</x:v>
+      </x:c>
+      <x:c r="S12" s="2" t="n">
         <x:v>0.06</x:v>
       </x:c>
-      <x:c r="P12" s="2" t="n">
+      <x:c r="T12" s="2" t="n">
         <x:v>0.08</x:v>
       </x:c>
-      <x:c r="Q12" s="2" t="n">
-        <x:v>1.8</x:v>
-      </x:c>
-      <x:c r="R12" s="2" t="n">
-        <x:v>1.12</x:v>
-      </x:c>
-      <x:c r="S12" s="2" t="n">
-        <x:v>0.035</x:v>
-      </x:c>
-      <x:c r="T12" s="2" t="n">
-        <x:v>0.04</x:v>
-      </x:c>
       <x:c r="U12" s="2" t="n">
-        <x:v>1.5</x:v>
+        <x:v>2.05</x:v>
       </x:c>
       <x:c r="V12" s="2" t="n">
-        <x:v>1.05</x:v>
+        <x:v>1.02</x:v>
       </x:c>
       <x:c r="W12" s="2" t="n">
-        <x:v>0.01</x:v>
+        <x:v>0.012</x:v>
       </x:c>
       <x:c r="X12" s="2" t="n">
-        <x:v>0</x:v>
+        <x:v>0.025</x:v>
       </x:c>
       <x:c r="Y12" s="2" t="n">
-        <x:v>1.15</x:v>
+        <x:v>1.3</x:v>
       </x:c>
       <x:c r="Z12" s="2" t="n">
-        <x:v>1.2</x:v>
+        <x:v>1.25</x:v>
       </x:c>
       <x:c r="AA12" s="2" t="n">
-        <x:v>0.05</x:v>
+        <x:v>0.07</x:v>
       </x:c>
       <x:c r="AB12" s="2" t="n">
-        <x:v>0.05</x:v>
+        <x:v>0.08</x:v>
       </x:c>
       <x:c r="AC12" s="2" t="n">
-        <x:v>1.7</x:v>
+        <x:v>2.2</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -1333,70 +1333,70 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="H13" s="2" t="n">
-        <x:v>34</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="I13" s="2" t="n">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="J13" s="2" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="K13" s="2" t="n">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="L13" s="2" t="n">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="M13" s="2" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="N13" s="2" t="n">
+        <x:v>1.35</x:v>
+      </x:c>
+      <x:c r="O13" s="2" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="P13" s="2" t="n">
+        <x:v>0.2</x:v>
+      </x:c>
+      <x:c r="Q13" s="2" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="K13" s="2" t="n">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="L13" s="2" t="n">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="M13" s="2" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="N13" s="2" t="n">
-        <x:v>1.25</x:v>
-      </x:c>
-      <x:c r="O13" s="2" t="n">
-        <x:v>0.06</x:v>
-      </x:c>
-      <x:c r="P13" s="2" t="n">
+      <x:c r="R13" s="2" t="n">
+        <x:v>1.3</x:v>
+      </x:c>
+      <x:c r="S13" s="2" t="n">
+        <x:v>0.07</x:v>
+      </x:c>
+      <x:c r="T13" s="2" t="n">
+        <x:v>0.12</x:v>
+      </x:c>
+      <x:c r="U13" s="2" t="n">
+        <x:v>2.4</x:v>
+      </x:c>
+      <x:c r="V13" s="2" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="W13" s="2" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="X13" s="2" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="Y13" s="2" t="n">
+        <x:v>1.15</x:v>
+      </x:c>
+      <x:c r="Z13" s="2" t="n">
+        <x:v>1.3</x:v>
+      </x:c>
+      <x:c r="AA13" s="2" t="n">
         <x:v>0.1</x:v>
       </x:c>
-      <x:c r="Q13" s="2" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="R13" s="2" t="n">
-        <x:v>1.12</x:v>
-      </x:c>
-      <x:c r="S13" s="2" t="n">
-        <x:v>0.035</x:v>
-      </x:c>
-      <x:c r="T13" s="2" t="n">
-        <x:v>0.04</x:v>
-      </x:c>
-      <x:c r="U13" s="2" t="n">
-        <x:v>1.5</x:v>
-      </x:c>
-      <x:c r="V13" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="W13" s="2" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="X13" s="2" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="Y13" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="Z13" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AA13" s="2" t="n">
-        <x:v>0.08</x:v>
-      </x:c>
       <x:c r="AB13" s="2" t="n">
-        <x:v>0.1</x:v>
+        <x:v>0.12</x:v>
       </x:c>
       <x:c r="AC13" s="2" t="n">
-        <x:v>2</x:v>
+        <x:v>2.8</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/FPSDemo/MiniTemplate/Datas/#enemy_spawn_pool.xlsx
+++ b/FPSDemo/MiniTemplate/Datas/#enemy_spawn_pool.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="enemy_spawn_pool" sheetId="1" r:id="R27e692c0dee24c39"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="enemy_spawn_pool" sheetId="1" r:id="R15466ff721964f58"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1180,37 +1180,37 @@
         <x:v>1.2</x:v>
       </x:c>
       <x:c r="O11" s="2" t="n">
-        <x:v>0.09</x:v>
+        <x:v>0.18</x:v>
       </x:c>
       <x:c r="P11" s="2" t="n">
         <x:v>0.15</x:v>
       </x:c>
       <x:c r="Q11" s="2" t="n">
-        <x:v>2.6</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="R11" s="2" t="n">
         <x:v>1.15</x:v>
       </x:c>
       <x:c r="S11" s="2" t="n">
-        <x:v>0.06</x:v>
+        <x:v>0.13</x:v>
       </x:c>
       <x:c r="T11" s="2" t="n">
         <x:v>0.08</x:v>
       </x:c>
       <x:c r="U11" s="2" t="n">
-        <x:v>2.1</x:v>
+        <x:v>3.8</x:v>
       </x:c>
       <x:c r="V11" s="2" t="n">
         <x:v>1.04</x:v>
       </x:c>
       <x:c r="W11" s="2" t="n">
-        <x:v>0.015</x:v>
+        <x:v>0.012</x:v>
       </x:c>
       <x:c r="X11" s="2" t="n">
         <x:v>0.02</x:v>
       </x:c>
       <x:c r="Y11" s="2" t="n">
-        <x:v>1.22</x:v>
+        <x:v>1.2</x:v>
       </x:c>
       <x:c r="Z11" s="2" t="n">
         <x:v>1.25</x:v>
@@ -1267,37 +1267,37 @@
         <x:v>1.25</x:v>
       </x:c>
       <x:c r="O12" s="2" t="n">
-        <x:v>0.09</x:v>
+        <x:v>0.16</x:v>
       </x:c>
       <x:c r="P12" s="2" t="n">
         <x:v>0.15</x:v>
       </x:c>
       <x:c r="Q12" s="2" t="n">
-        <x:v>2.5</x:v>
+        <x:v>4.5</x:v>
       </x:c>
       <x:c r="R12" s="2" t="n">
         <x:v>1.2</x:v>
       </x:c>
       <x:c r="S12" s="2" t="n">
-        <x:v>0.06</x:v>
+        <x:v>0.12</x:v>
       </x:c>
       <x:c r="T12" s="2" t="n">
         <x:v>0.08</x:v>
       </x:c>
       <x:c r="U12" s="2" t="n">
-        <x:v>2.05</x:v>
+        <x:v>3.5</x:v>
       </x:c>
       <x:c r="V12" s="2" t="n">
         <x:v>1.02</x:v>
       </x:c>
       <x:c r="W12" s="2" t="n">
-        <x:v>0.012</x:v>
+        <x:v>0.005</x:v>
       </x:c>
       <x:c r="X12" s="2" t="n">
-        <x:v>0.025</x:v>
+        <x:v>0.01</x:v>
       </x:c>
       <x:c r="Y12" s="2" t="n">
-        <x:v>1.3</x:v>
+        <x:v>1.15</x:v>
       </x:c>
       <x:c r="Z12" s="2" t="n">
         <x:v>1.25</x:v>
@@ -1354,37 +1354,37 @@
         <x:v>1.35</x:v>
       </x:c>
       <x:c r="O13" s="2" t="n">
-        <x:v>0.1</x:v>
+        <x:v>0.22</x:v>
       </x:c>
       <x:c r="P13" s="2" t="n">
         <x:v>0.2</x:v>
       </x:c>
       <x:c r="Q13" s="2" t="n">
-        <x:v>3</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="R13" s="2" t="n">
         <x:v>1.3</x:v>
       </x:c>
       <x:c r="S13" s="2" t="n">
-        <x:v>0.07</x:v>
+        <x:v>0.16</x:v>
       </x:c>
       <x:c r="T13" s="2" t="n">
         <x:v>0.12</x:v>
       </x:c>
       <x:c r="U13" s="2" t="n">
-        <x:v>2.4</x:v>
+        <x:v>4.8</x:v>
       </x:c>
       <x:c r="V13" s="2" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="W13" s="2" t="n">
-        <x:v>0.01</x:v>
+        <x:v>0.008</x:v>
       </x:c>
       <x:c r="X13" s="2" t="n">
         <x:v>0.02</x:v>
       </x:c>
       <x:c r="Y13" s="2" t="n">
-        <x:v>1.15</x:v>
+        <x:v>1.12</x:v>
       </x:c>
       <x:c r="Z13" s="2" t="n">
         <x:v>1.3</x:v>
